--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11057" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -842,8 +842,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -1212,7 +1212,7 @@
   </si>
   <si>
     <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1535,10 +1535,6 @@
   </si>
   <si>
     <t>Practitioner.identifier:idNatPs.type</t>
-  </si>
-  <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -1691,7 +1687,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="http://interopsante.org/fhir/CodeSystem/fr-v2-0203"/&gt;
+    &lt;system value="https://hl7.fr/ig/fhir/core/CodeSystem/fr-core-cs-v2-0203"/&gt;
     &lt;code value="INTRN"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1715,7 +1711,19 @@
     <t>Practitioner.identifier:identifiantInterne.period</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
     <t>Practitioner.identifier:identifiantInterne.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Practitioner.active</t>
@@ -6076,7 +6084,7 @@
         <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>119</v>
@@ -6088,7 +6096,7 @@
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>78</v>
@@ -6193,7 +6201,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>119</v>
@@ -6423,7 +6431,7 @@
         <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>119</v>
@@ -6653,7 +6661,7 @@
         <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>102</v>
@@ -6770,7 +6778,7 @@
         <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>119</v>
@@ -7000,7 +7008,7 @@
         <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>119</v>
@@ -7230,7 +7238,7 @@
         <v>90</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>102</v>
@@ -7347,7 +7355,7 @@
         <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>119</v>
@@ -7577,7 +7585,7 @@
         <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>119</v>
@@ -7809,7 +7817,7 @@
         <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>102</v>
@@ -8041,7 +8049,7 @@
         <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>119</v>
@@ -8053,7 +8061,7 @@
         <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -8394,7 +8402,7 @@
         <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>119</v>
@@ -8624,7 +8632,7 @@
         <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>119</v>
@@ -8854,7 +8862,7 @@
         <v>90</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>102</v>
@@ -8971,7 +8979,7 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>119</v>
@@ -9201,7 +9209,7 @@
         <v>80</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>119</v>
@@ -9431,7 +9439,7 @@
         <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>102</v>
@@ -9548,7 +9556,7 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>119</v>
@@ -9778,7 +9786,7 @@
         <v>80</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>119</v>
@@ -10010,7 +10018,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -10242,7 +10250,7 @@
         <v>90</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>102</v>
@@ -10591,7 +10599,7 @@
         <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>119</v>
@@ -10603,7 +10611,7 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10708,7 +10716,7 @@
         <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>119</v>
@@ -10938,7 +10946,7 @@
         <v>80</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>119</v>
@@ -11168,7 +11176,7 @@
         <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>102</v>
@@ -11285,7 +11293,7 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>119</v>
@@ -11515,7 +11523,7 @@
         <v>80</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>119</v>
@@ -11747,7 +11755,7 @@
         <v>90</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>102</v>
@@ -11979,7 +11987,7 @@
         <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>119</v>
@@ -11991,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -12332,7 +12340,7 @@
         <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>119</v>
@@ -12562,7 +12570,7 @@
         <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>119</v>
@@ -12792,7 +12800,7 @@
         <v>90</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>102</v>
@@ -12909,7 +12917,7 @@
         <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>119</v>
@@ -13139,7 +13147,7 @@
         <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>119</v>
@@ -13369,7 +13377,7 @@
         <v>90</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>102</v>
@@ -13601,7 +13609,7 @@
         <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>102</v>
@@ -16820,7 +16828,7 @@
         <v>233</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>491</v>
+        <v>384</v>
       </c>
       <c r="M116" t="s" s="2">
         <v>385</v>
@@ -16839,7 +16847,7 @@
         <v>78</v>
       </c>
       <c r="S116" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="T116" t="s" s="2">
         <v>78</v>
@@ -16857,10 +16865,10 @@
         <v>158</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -16910,7 +16918,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>449</v>
@@ -16942,7 +16950,7 @@
         <v>450</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>452</v>
@@ -16958,7 +16966,7 @@
         <v>78</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>454</v>
@@ -17029,7 +17037,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>459</v>
@@ -17058,7 +17066,7 @@
         <v>104</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M118" t="s" s="2">
         <v>461</v>
@@ -17146,7 +17154,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>468</v>
@@ -17261,7 +17269,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>475</v>
@@ -17378,13 +17386,13 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D121" t="s" s="2">
         <v>78</v>
@@ -17409,7 +17417,7 @@
         <v>362</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="M121" t="s" s="2">
         <v>364</v>
@@ -17497,7 +17505,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>372</v>
@@ -17612,7 +17620,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>373</v>
@@ -17729,7 +17737,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>374</v>
@@ -17848,7 +17856,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>383</v>
@@ -17877,7 +17885,7 @@
         <v>233</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>385</v>
@@ -17896,7 +17904,7 @@
         <v>78</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>78</v>
@@ -17914,10 +17922,10 @@
         <v>158</v>
       </c>
       <c r="Y125" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z125" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17967,7 +17975,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>449</v>
@@ -17999,7 +18007,7 @@
         <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>452</v>
@@ -18015,7 +18023,7 @@
         <v>78</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>454</v>
@@ -18086,7 +18094,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>459</v>
@@ -18203,7 +18211,7 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>468</v>
@@ -18318,7 +18326,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>475</v>
@@ -18435,13 +18443,13 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>78</v>
@@ -18466,7 +18474,7 @@
         <v>362</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="M130" t="s" s="2">
         <v>364</v>
@@ -18554,7 +18562,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>372</v>
@@ -18669,7 +18677,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>373</v>
@@ -18786,7 +18794,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>374</v>
@@ -18905,7 +18913,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>383</v>
@@ -18934,7 +18942,7 @@
         <v>233</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M134" t="s" s="2">
         <v>385</v>
@@ -18953,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="S134" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T134" t="s" s="2">
         <v>78</v>
@@ -18971,10 +18979,10 @@
         <v>158</v>
       </c>
       <c r="Y134" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z134" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>78</v>
@@ -19024,7 +19032,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>449</v>
@@ -19056,7 +19064,7 @@
         <v>450</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>452</v>
@@ -19072,7 +19080,7 @@
         <v>78</v>
       </c>
       <c r="S135" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="T135" t="s" s="2">
         <v>454</v>
@@ -19143,7 +19151,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>459</v>
@@ -19260,7 +19268,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>468</v>
@@ -19375,7 +19383,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>475</v>
@@ -19492,13 +19500,13 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>361</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="D139" t="s" s="2">
         <v>78</v>
@@ -19523,7 +19531,7 @@
         <v>362</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="M139" t="s" s="2">
         <v>364</v>
@@ -19611,7 +19619,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B140" t="s" s="2">
         <v>372</v>
@@ -19726,7 +19734,7 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B141" t="s" s="2">
         <v>373</v>
@@ -19820,7 +19828,7 @@
         <v>80</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ141" t="s" s="2">
         <v>119</v>
@@ -19832,7 +19840,7 @@
         <v>78</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19843,7 +19851,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B142" t="s" s="2">
         <v>374</v>
@@ -19939,7 +19947,7 @@
         <v>90</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>102</v>
@@ -19962,7 +19970,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>383</v>
@@ -19991,7 +19999,7 @@
         <v>233</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M143" t="s" s="2">
         <v>385</v>
@@ -20010,7 +20018,7 @@
         <v>78</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>78</v>
@@ -20028,10 +20036,10 @@
         <v>158</v>
       </c>
       <c r="Y143" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z143" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>78</v>
@@ -20058,7 +20066,7 @@
         <v>90</v>
       </c>
       <c r="AI143" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ143" t="s" s="2">
         <v>102</v>
@@ -20081,7 +20089,7 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>449</v>
@@ -20110,10 +20118,10 @@
         <v>137</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>452</v>
@@ -20148,7 +20156,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>78</v>
@@ -20175,7 +20183,7 @@
         <v>90</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>102</v>
@@ -20198,7 +20206,7 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>459</v>
@@ -20227,7 +20235,7 @@
         <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>461</v>
@@ -20292,7 +20300,7 @@
         <v>90</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>102</v>
@@ -20315,7 +20323,7 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>468</v>
@@ -20349,7 +20357,9 @@
       <c r="M146" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="N146" s="2"/>
+      <c r="N146" t="s" s="2">
+        <v>542</v>
+      </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20407,10 +20417,10 @@
         <v>90</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>102</v>
+        <v>543</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
@@ -20430,7 +20440,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>475</v>
@@ -20524,10 +20534,10 @@
         <v>90</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>102</v>
+        <v>545</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
@@ -20547,10 +20557,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20576,67 +20586,67 @@
         <v>297</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M148" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q148" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="R148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF148" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="P148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q148" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="R148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE148" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF148" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20657,21 +20667,21 @@
         <v>78</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO148" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20694,19 +20704,19 @@
         <v>78</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20755,7 +20765,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20773,13 +20783,13 @@
         <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AO149" t="s" s="2">
         <v>78</v>
@@ -20787,10 +20797,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20902,10 +20912,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21019,13 +21029,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -21047,13 +21057,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21136,10 +21146,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21165,16 +21175,16 @@
         <v>176</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
@@ -21203,7 +21213,7 @@
       </c>
       <c r="Y153" s="2"/>
       <c r="Z153" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>78</v>
@@ -21221,7 +21231,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -21239,13 +21249,13 @@
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>78</v>
@@ -21253,10 +21263,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21282,16 +21292,16 @@
         <v>104</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
@@ -21340,7 +21350,7 @@
         <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -21358,10 +21368,10 @@
         <v>78</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>78</v>
@@ -21372,14 +21382,14 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -21401,13 +21411,13 @@
         <v>104</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21457,7 +21467,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>79</v>
@@ -21475,13 +21485,13 @@
         <v>78</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>78</v>
@@ -21489,14 +21499,14 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -21518,13 +21528,13 @@
         <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -21574,7 +21584,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21592,13 +21602,13 @@
         <v>78</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>78</v>
@@ -21606,10 +21616,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21635,10 +21645,10 @@
         <v>104</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -21668,10 +21678,10 @@
         <v>158</v>
       </c>
       <c r="Y157" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>78</v>
@@ -21689,7 +21699,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21707,13 +21717,13 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>78</v>
@@ -21721,10 +21731,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21750,10 +21760,10 @@
         <v>104</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -21783,10 +21793,10 @@
         <v>158</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>78</v>
@@ -21804,7 +21814,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21822,10 +21832,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21836,10 +21846,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21865,14 +21875,14 @@
         <v>253</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21921,7 +21931,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21939,10 +21949,10 @@
         <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>474</v>
@@ -21953,10 +21963,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21979,19 +21989,19 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>78</v>
@@ -22028,17 +22038,17 @@
         <v>78</v>
       </c>
       <c r="AB160" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AC160" s="2"/>
       <c r="AD160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE160" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>79</v>
@@ -22050,19 +22060,19 @@
         <v>209</v>
       </c>
       <c r="AJ160" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AK160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>78</v>
@@ -22070,13 +22080,13 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D161" t="s" s="2">
         <v>78</v>
@@ -22098,19 +22108,19 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="O161" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>78</v>
@@ -22159,7 +22169,7 @@
         <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
@@ -22171,19 +22181,19 @@
         <v>209</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL161" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>78</v>
@@ -22191,10 +22201,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22306,10 +22316,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22423,13 +22433,13 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
@@ -22451,13 +22461,13 @@
         <v>78</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -22540,10 +22550,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22655,10 +22665,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22770,10 +22780,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22813,7 +22823,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>78</v>
@@ -22887,10 +22897,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22931,7 +22941,7 @@
         <v>78</v>
       </c>
       <c r="S168" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="T168" t="s" s="2">
         <v>78</v>
@@ -22950,7 +22960,7 @@
       </c>
       <c r="Y168" s="2"/>
       <c r="Z168" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AA168" t="s" s="2">
         <v>78</v>
@@ -23000,13 +23010,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -23028,13 +23038,13 @@
         <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -23117,10 +23127,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23232,10 +23242,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23326,7 +23336,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>119</v>
@@ -23338,7 +23348,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -23349,10 +23359,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>312</v>
@@ -23380,7 +23390,7 @@
         <v>111</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="M172" t="s" s="2">
         <v>202</v>
@@ -23443,7 +23453,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>119</v>
@@ -23466,10 +23476,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23581,10 +23591,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23673,7 +23683,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>119</v>
@@ -23696,10 +23706,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23813,10 +23823,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23876,7 +23886,7 @@
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23903,7 +23913,7 @@
         <v>90</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>102</v>
@@ -23926,13 +23936,13 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
@@ -23957,7 +23967,7 @@
         <v>111</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>202</v>
@@ -24020,7 +24030,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>119</v>
@@ -24043,10 +24053,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24158,10 +24168,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24250,7 +24260,7 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>119</v>
@@ -24273,10 +24283,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24316,7 +24326,7 @@
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -24390,10 +24400,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24482,7 +24492,7 @@
         <v>90</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>102</v>
@@ -24505,13 +24515,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24599,7 +24609,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>119</v>
@@ -24622,10 +24632,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24737,10 +24747,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24829,7 +24839,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>119</v>
@@ -24852,10 +24862,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24895,7 +24905,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24969,10 +24979,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25061,7 +25071,7 @@
         <v>90</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>102</v>
@@ -25084,13 +25094,13 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
@@ -25115,7 +25125,7 @@
         <v>111</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="M187" t="s" s="2">
         <v>202</v>
@@ -25178,7 +25188,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>119</v>
@@ -25201,10 +25211,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25316,10 +25326,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25408,7 +25418,7 @@
         <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>119</v>
@@ -25431,10 +25441,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25474,7 +25484,7 @@
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25548,10 +25558,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25640,7 +25650,7 @@
         <v>90</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>102</v>
@@ -25663,13 +25673,13 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D192" t="s" s="2">
         <v>78</v>
@@ -25757,7 +25767,7 @@
         <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ192" t="s" s="2">
         <v>119</v>
@@ -25780,10 +25790,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25895,10 +25905,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -25987,7 +25997,7 @@
         <v>80</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>119</v>
@@ -26010,10 +26020,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26053,7 +26063,7 @@
       </c>
       <c r="Q195" s="2"/>
       <c r="R195" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="S195" t="s" s="2">
         <v>78</v>
@@ -26127,10 +26137,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26219,7 +26229,7 @@
         <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ196" t="s" s="2">
         <v>102</v>
@@ -26242,13 +26252,13 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>78</v>
@@ -26273,7 +26283,7 @@
         <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M197" t="s" s="2">
         <v>202</v>
@@ -26336,7 +26346,7 @@
         <v>80</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>119</v>
@@ -26359,10 +26369,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26474,10 +26484,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26566,7 +26576,7 @@
         <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ199" t="s" s="2">
         <v>119</v>
@@ -26589,10 +26599,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26632,7 +26642,7 @@
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="S200" t="s" s="2">
         <v>78</v>
@@ -26706,10 +26716,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26798,7 +26808,7 @@
         <v>90</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>102</v>
@@ -26821,13 +26831,13 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>78</v>
@@ -26852,7 +26862,7 @@
         <v>111</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="M202" t="s" s="2">
         <v>202</v>
@@ -26915,7 +26925,7 @@
         <v>80</v>
       </c>
       <c r="AI202" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ202" t="s" s="2">
         <v>119</v>
@@ -26938,10 +26948,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27053,10 +27063,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27145,7 +27155,7 @@
         <v>80</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>119</v>
@@ -27168,10 +27178,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27211,7 +27221,7 @@
       </c>
       <c r="Q205" s="2"/>
       <c r="R205" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="S205" t="s" s="2">
         <v>78</v>
@@ -27285,10 +27295,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27377,7 +27387,7 @@
         <v>90</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ206" t="s" s="2">
         <v>102</v>
@@ -27400,10 +27410,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27443,7 +27453,7 @@
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="S207" t="s" s="2">
         <v>78</v>
@@ -27517,10 +27527,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27609,7 +27619,7 @@
         <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>102</v>
@@ -27632,10 +27642,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27661,10 +27671,10 @@
         <v>176</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="N209" s="2"/>
       <c r="O209" s="2"/>
@@ -27676,7 +27686,7 @@
         <v>78</v>
       </c>
       <c r="S209" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="T209" t="s" s="2">
         <v>78</v>
@@ -27694,10 +27704,10 @@
         <v>236</v>
       </c>
       <c r="Y209" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="Z209" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="AA209" t="s" s="2">
         <v>78</v>
@@ -27715,7 +27725,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27724,7 +27734,7 @@
         <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="AJ209" t="s" s="2">
         <v>102</v>
@@ -27733,13 +27743,13 @@
         <v>78</v>
       </c>
       <c r="AL209" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AN209" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="AO209" t="s" s="2">
         <v>78</v>
@@ -27747,10 +27757,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27776,16 +27786,16 @@
         <v>104</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27834,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27852,10 +27862,10 @@
         <v>78</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>467</v>
@@ -27866,10 +27876,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27895,16 +27905,16 @@
         <v>176</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>78</v>
@@ -27932,10 +27942,10 @@
         <v>236</v>
       </c>
       <c r="Y211" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="Z211" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27953,7 +27963,7 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
@@ -27971,13 +27981,13 @@
         <v>78</v>
       </c>
       <c r="AL211" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN211" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AO211" t="s" s="2">
         <v>78</v>
@@ -27985,10 +27995,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28011,16 +28021,16 @@
         <v>91</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
@@ -28070,7 +28080,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -28102,10 +28112,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28131,10 +28141,10 @@
         <v>253</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28185,7 +28195,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -28206,7 +28216,7 @@
         <v>199</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>474</v>
@@ -28217,10 +28227,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28243,19 +28253,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -28304,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -28322,13 +28332,13 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>78</v>
@@ -28336,10 +28346,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28365,14 +28375,14 @@
         <v>176</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28400,10 +28410,10 @@
         <v>236</v>
       </c>
       <c r="Y215" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="Z215" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AA215" t="s" s="2">
         <v>78</v>
@@ -28421,7 +28431,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28439,13 +28449,13 @@
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28453,10 +28463,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28479,17 +28489,17 @@
         <v>91</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28538,7 +28548,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28556,13 +28566,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28570,10 +28580,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28596,17 +28606,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28655,7 +28665,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28676,10 +28686,10 @@
         <v>78</v>
       </c>
       <c r="AM217" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>78</v>
@@ -28687,10 +28697,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -28713,13 +28723,13 @@
         <v>78</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N218" s="2"/>
       <c r="O218" s="2"/>
@@ -28758,7 +28768,7 @@
         <v>78</v>
       </c>
       <c r="AB218" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AC218" s="2"/>
       <c r="AD218" t="s" s="2">
@@ -28768,7 +28778,7 @@
         <v>117</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>79</v>
@@ -28786,13 +28796,13 @@
         <v>78</v>
       </c>
       <c r="AL218" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>78</v>
@@ -28800,10 +28810,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -28915,10 +28925,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29032,14 +29042,14 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E221" s="2"/>
       <c r="F221" t="s" s="2">
@@ -29061,10 +29071,10 @@
         <v>111</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N221" t="s" s="2">
         <v>114</v>
@@ -29119,7 +29129,7 @@
         <v>78</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>79</v>
@@ -29151,10 +29161,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29180,14 +29190,14 @@
         <v>362</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P222" t="s" s="2">
         <v>78</v>
@@ -29236,7 +29246,7 @@
         <v>78</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>79</v>
@@ -29257,7 +29267,7 @@
         <v>78</v>
       </c>
       <c r="AM222" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AN222" t="s" s="2">
         <v>78</v>
@@ -29268,10 +29278,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -29297,10 +29307,10 @@
         <v>233</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -29331,7 +29341,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>78</v>
@@ -29349,7 +29359,7 @@
         <v>78</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>90</v>
@@ -29370,10 +29380,10 @@
         <v>78</v>
       </c>
       <c r="AM223" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN223" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AO223" t="s" s="2">
         <v>78</v>
@@ -29381,10 +29391,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29410,14 +29420,14 @@
         <v>253</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P224" t="s" s="2">
         <v>78</v>
@@ -29466,7 +29476,7 @@
         <v>78</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>79</v>
@@ -29487,10 +29497,10 @@
         <v>78</v>
       </c>
       <c r="AM224" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AN224" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AO224" t="s" s="2">
         <v>78</v>
@@ -29498,10 +29508,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29527,10 +29537,10 @@
         <v>476</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -29581,7 +29591,7 @@
         <v>78</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>79</v>
@@ -29602,7 +29612,7 @@
         <v>78</v>
       </c>
       <c r="AM225" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>78</v>
@@ -29613,13 +29623,13 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D226" t="s" s="2">
         <v>78</v>
@@ -29641,13 +29651,13 @@
         <v>78</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -29698,7 +29708,7 @@
         <v>78</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>79</v>
@@ -29716,13 +29726,13 @@
         <v>78</v>
       </c>
       <c r="AL226" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN226" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AO226" t="s" s="2">
         <v>78</v>
@@ -29730,10 +29740,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -29845,10 +29855,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -29958,13 +29968,13 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D229" t="s" s="2">
         <v>78</v>
@@ -29986,13 +29996,13 @@
         <v>78</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
@@ -30075,10 +30085,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30190,10 +30200,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30284,7 +30294,7 @@
         <v>80</v>
       </c>
       <c r="AI231" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ231" t="s" s="2">
         <v>119</v>
@@ -30296,7 +30306,7 @@
         <v>78</v>
       </c>
       <c r="AM231" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN231" t="s" s="2">
         <v>78</v>
@@ -30307,13 +30317,13 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D232" t="s" s="2">
         <v>78</v>
@@ -30401,7 +30411,7 @@
         <v>80</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ232" t="s" s="2">
         <v>119</v>
@@ -30424,10 +30434,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30539,10 +30549,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30631,7 +30641,7 @@
         <v>80</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>119</v>
@@ -30654,10 +30664,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30697,7 +30707,7 @@
       </c>
       <c r="Q235" s="2"/>
       <c r="R235" t="s" s="2">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="S235" t="s" s="2">
         <v>78</v>
@@ -30771,10 +30781,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -30834,7 +30844,7 @@
       </c>
       <c r="Y236" s="2"/>
       <c r="Z236" t="s" s="2">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="AA236" t="s" s="2">
         <v>78</v>
@@ -30861,7 +30871,7 @@
         <v>90</v>
       </c>
       <c r="AI236" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ236" t="s" s="2">
         <v>102</v>
@@ -30884,13 +30894,13 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="D237" t="s" s="2">
         <v>78</v>
@@ -30978,7 +30988,7 @@
         <v>80</v>
       </c>
       <c r="AI237" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ237" t="s" s="2">
         <v>119</v>
@@ -31001,10 +31011,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -31116,10 +31126,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -31208,7 +31218,7 @@
         <v>80</v>
       </c>
       <c r="AI239" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ239" t="s" s="2">
         <v>119</v>
@@ -31231,10 +31241,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -31274,7 +31284,7 @@
       </c>
       <c r="Q240" s="2"/>
       <c r="R240" t="s" s="2">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="S240" t="s" s="2">
         <v>78</v>
@@ -31348,10 +31358,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -31411,7 +31421,7 @@
       </c>
       <c r="Y241" s="2"/>
       <c r="Z241" t="s" s="2">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="AA241" t="s" s="2">
         <v>78</v>
@@ -31438,7 +31448,7 @@
         <v>90</v>
       </c>
       <c r="AI241" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ241" t="s" s="2">
         <v>102</v>
@@ -31461,13 +31471,13 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D242" t="s" s="2">
         <v>78</v>
@@ -31555,7 +31565,7 @@
         <v>80</v>
       </c>
       <c r="AI242" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ242" t="s" s="2">
         <v>119</v>
@@ -31578,10 +31588,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -31693,10 +31703,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -31785,7 +31795,7 @@
         <v>80</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>119</v>
@@ -31808,10 +31818,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -31851,7 +31861,7 @@
       </c>
       <c r="Q245" s="2"/>
       <c r="R245" t="s" s="2">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="S245" t="s" s="2">
         <v>78</v>
@@ -31925,10 +31935,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -31988,7 +31998,7 @@
       </c>
       <c r="Y246" s="2"/>
       <c r="Z246" t="s" s="2">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="AA246" t="s" s="2">
         <v>78</v>
@@ -32015,7 +32025,7 @@
         <v>90</v>
       </c>
       <c r="AI246" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ246" t="s" s="2">
         <v>102</v>
@@ -32038,10 +32048,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -32081,7 +32091,7 @@
       </c>
       <c r="Q247" s="2"/>
       <c r="R247" t="s" s="2">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="S247" t="s" s="2">
         <v>78</v>
@@ -32155,10 +32165,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -32247,7 +32257,7 @@
         <v>90</v>
       </c>
       <c r="AI248" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ248" t="s" s="2">
         <v>102</v>
@@ -32270,14 +32280,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -32299,10 +32309,10 @@
         <v>111</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>114</v>
@@ -32357,7 +32367,7 @@
         <v>78</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>79</v>
@@ -32389,10 +32399,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -32418,14 +32428,14 @@
         <v>362</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P250" t="s" s="2">
         <v>78</v>
@@ -32474,7 +32484,7 @@
         <v>78</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>79</v>
@@ -32495,7 +32505,7 @@
         <v>78</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>78</v>
@@ -32506,10 +32516,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -32535,10 +32545,10 @@
         <v>233</v>
       </c>
       <c r="L251" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M251" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N251" s="2"/>
       <c r="O251" s="2"/>
@@ -32569,7 +32579,7 @@
       </c>
       <c r="Y251" s="2"/>
       <c r="Z251" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA251" t="s" s="2">
         <v>78</v>
@@ -32587,7 +32597,7 @@
         <v>78</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>90</v>
@@ -32608,10 +32618,10 @@
         <v>78</v>
       </c>
       <c r="AM251" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN251" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AO251" t="s" s="2">
         <v>78</v>
@@ -32619,10 +32629,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -32734,10 +32744,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -32828,7 +32838,7 @@
         <v>80</v>
       </c>
       <c r="AI253" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ253" t="s" s="2">
         <v>119</v>
@@ -32840,7 +32850,7 @@
         <v>78</v>
       </c>
       <c r="AM253" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN253" t="s" s="2">
         <v>78</v>
@@ -32851,10 +32861,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -32926,14 +32936,14 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE254" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AF254" t="s" s="2">
         <v>398</v>
@@ -32945,7 +32955,7 @@
         <v>80</v>
       </c>
       <c r="AI254" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ254" t="s" s="2">
         <v>102</v>
@@ -32968,13 +32978,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B255" t="s" s="2">
         <v>891</v>
       </c>
-      <c r="B255" t="s" s="2">
-        <v>889</v>
-      </c>
       <c r="C255" t="s" s="2">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33037,7 +33047,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33064,7 +33074,7 @@
         <v>80</v>
       </c>
       <c r="AI255" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ255" t="s" s="2">
         <v>102</v>
@@ -33087,13 +33097,13 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>78</v>
@@ -33156,7 +33166,7 @@
       </c>
       <c r="Y256" s="2"/>
       <c r="Z256" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA256" t="s" s="2">
         <v>78</v>
@@ -33183,7 +33193,7 @@
         <v>80</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ256" t="s" s="2">
         <v>102</v>
@@ -33206,10 +33216,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33302,7 +33312,7 @@
         <v>90</v>
       </c>
       <c r="AI257" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ257" t="s" s="2">
         <v>102</v>
@@ -33325,10 +33335,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -33354,14 +33364,14 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N258" s="2"/>
       <c r="O258" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P258" t="s" s="2">
         <v>78</v>
@@ -33410,7 +33420,7 @@
         <v>78</v>
       </c>
       <c r="AF258" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG258" t="s" s="2">
         <v>79</v>
@@ -33431,10 +33441,10 @@
         <v>78</v>
       </c>
       <c r="AM258" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AN258" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AO258" t="s" s="2">
         <v>78</v>
@@ -33442,10 +33452,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33557,10 +33567,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33651,7 +33661,7 @@
         <v>80</v>
       </c>
       <c r="AI260" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ260" t="s" s="2">
         <v>119</v>
@@ -33663,7 +33673,7 @@
         <v>78</v>
       </c>
       <c r="AM260" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN260" t="s" s="2">
         <v>78</v>
@@ -33674,10 +33684,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33703,7 +33713,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33791,10 +33801,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33820,7 +33830,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33910,10 +33920,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -33936,13 +33946,13 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="L263" t="s" s="2">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="M263" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
@@ -33993,7 +34003,7 @@
         <v>78</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>79</v>
@@ -34014,7 +34024,7 @@
         <v>78</v>
       </c>
       <c r="AM263" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AN263" t="s" s="2">
         <v>78</v>
@@ -34025,13 +34035,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34053,13 +34063,13 @@
         <v>78</v>
       </c>
       <c r="K264" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="M264" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N264" s="2"/>
       <c r="O264" s="2"/>
@@ -34110,7 +34120,7 @@
         <v>78</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>79</v>
@@ -34128,13 +34138,13 @@
         <v>78</v>
       </c>
       <c r="AL264" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM264" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN264" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AO264" t="s" s="2">
         <v>78</v>
@@ -34142,10 +34152,10 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -34257,10 +34267,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -34374,14 +34384,14 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" t="s" s="2">
@@ -34403,10 +34413,10 @@
         <v>111</v>
       </c>
       <c r="L267" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M267" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N267" t="s" s="2">
         <v>114</v>
@@ -34461,7 +34471,7 @@
         <v>78</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>79</v>
@@ -34493,10 +34503,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -34522,14 +34532,14 @@
         <v>362</v>
       </c>
       <c r="L268" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M268" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N268" s="2"/>
       <c r="O268" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P268" t="s" s="2">
         <v>78</v>
@@ -34578,7 +34588,7 @@
         <v>78</v>
       </c>
       <c r="AF268" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG268" t="s" s="2">
         <v>79</v>
@@ -34599,7 +34609,7 @@
         <v>78</v>
       </c>
       <c r="AM268" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AN268" t="s" s="2">
         <v>78</v>
@@ -34610,10 +34620,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -34639,10 +34649,10 @@
         <v>233</v>
       </c>
       <c r="L269" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M269" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N269" s="2"/>
       <c r="O269" s="2"/>
@@ -34673,7 +34683,7 @@
       </c>
       <c r="Y269" s="2"/>
       <c r="Z269" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA269" t="s" s="2">
         <v>78</v>
@@ -34691,7 +34701,7 @@
         <v>78</v>
       </c>
       <c r="AF269" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AG269" t="s" s="2">
         <v>90</v>
@@ -34712,10 +34722,10 @@
         <v>78</v>
       </c>
       <c r="AM269" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN269" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AO269" t="s" s="2">
         <v>78</v>
@@ -34723,10 +34733,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -34838,10 +34848,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -34932,7 +34942,7 @@
         <v>80</v>
       </c>
       <c r="AI271" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ271" t="s" s="2">
         <v>119</v>
@@ -34944,7 +34954,7 @@
         <v>78</v>
       </c>
       <c r="AM271" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN271" t="s" s="2">
         <v>78</v>
@@ -34955,10 +34965,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -35030,14 +35040,14 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE272" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AF272" t="s" s="2">
         <v>398</v>
@@ -35049,7 +35059,7 @@
         <v>80</v>
       </c>
       <c r="AI272" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ272" t="s" s="2">
         <v>102</v>
@@ -35072,13 +35082,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35103,7 +35113,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35141,7 +35151,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35168,7 +35178,7 @@
         <v>80</v>
       </c>
       <c r="AI273" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ273" t="s" s="2">
         <v>102</v>
@@ -35191,10 +35201,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C274" t="s" s="2">
         <v>337</v>
@@ -35222,7 +35232,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35287,7 +35297,7 @@
         <v>80</v>
       </c>
       <c r="AI274" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ274" t="s" s="2">
         <v>102</v>
@@ -35310,10 +35320,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35406,7 +35416,7 @@
         <v>90</v>
       </c>
       <c r="AI275" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ275" t="s" s="2">
         <v>102</v>
@@ -35429,10 +35439,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -35458,14 +35468,14 @@
         <v>253</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M276" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N276" s="2"/>
       <c r="O276" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P276" t="s" s="2">
         <v>78</v>
@@ -35514,7 +35524,7 @@
         <v>78</v>
       </c>
       <c r="AF276" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG276" t="s" s="2">
         <v>79</v>
@@ -35535,10 +35545,10 @@
         <v>78</v>
       </c>
       <c r="AM276" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AN276" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AO276" t="s" s="2">
         <v>78</v>
@@ -35546,10 +35556,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35661,10 +35671,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35755,7 +35765,7 @@
         <v>80</v>
       </c>
       <c r="AI278" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ278" t="s" s="2">
         <v>119</v>
@@ -35767,7 +35777,7 @@
         <v>78</v>
       </c>
       <c r="AM278" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN278" t="s" s="2">
         <v>78</v>
@@ -35778,10 +35788,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35807,7 +35817,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35895,10 +35905,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35924,7 +35934,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36014,10 +36024,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -36043,10 +36053,10 @@
         <v>476</v>
       </c>
       <c r="L281" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="M281" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N281" s="2"/>
       <c r="O281" s="2"/>
@@ -36097,7 +36107,7 @@
         <v>78</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>79</v>
@@ -36118,7 +36128,7 @@
         <v>78</v>
       </c>
       <c r="AM281" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AN281" t="s" s="2">
         <v>78</v>
@@ -36129,13 +36139,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36157,13 +36167,13 @@
         <v>78</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="M282" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="N282" s="2"/>
       <c r="O282" s="2"/>
@@ -36214,7 +36224,7 @@
         <v>78</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>79</v>
@@ -36232,13 +36242,13 @@
         <v>78</v>
       </c>
       <c r="AL282" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="AM282" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN282" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="AO282" t="s" s="2">
         <v>78</v>
@@ -36246,10 +36256,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -36361,10 +36371,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -36478,14 +36488,14 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" t="s" s="2">
@@ -36507,10 +36517,10 @@
         <v>111</v>
       </c>
       <c r="L285" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="M285" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="N285" t="s" s="2">
         <v>114</v>
@@ -36565,7 +36575,7 @@
         <v>78</v>
       </c>
       <c r="AF285" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AG285" t="s" s="2">
         <v>79</v>
@@ -36597,10 +36607,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -36626,14 +36636,14 @@
         <v>362</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="M286" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="N286" s="2"/>
       <c r="O286" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="P286" t="s" s="2">
         <v>78</v>
@@ -36682,7 +36692,7 @@
         <v>78</v>
       </c>
       <c r="AF286" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="AG286" t="s" s="2">
         <v>79</v>
@@ -36703,7 +36713,7 @@
         <v>78</v>
       </c>
       <c r="AM286" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AN286" t="s" s="2">
         <v>78</v>
@@ -36714,10 +36724,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -36743,10 +36753,10 @@
         <v>233</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M287" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N287" s="2"/>
       <c r="O287" s="2"/>
@@ -36777,7 +36787,7 @@
       </c>
       <c r="Y287" s="2"/>
       <c r="Z287" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="AA287" t="s" s="2">
         <v>78</v>
@@ -36795,7 +36805,7 @@
         <v>78</v>
       </c>
       <c r="AF287" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AG287" t="s" s="2">
         <v>90</v>
@@ -36810,16 +36820,16 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM287" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="AN287" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="AO287" t="s" s="2">
         <v>78</v>
@@ -36827,10 +36837,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -36942,10 +36952,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -37036,7 +37046,7 @@
         <v>80</v>
       </c>
       <c r="AI289" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ289" t="s" s="2">
         <v>119</v>
@@ -37048,7 +37058,7 @@
         <v>78</v>
       </c>
       <c r="AM289" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN289" t="s" s="2">
         <v>78</v>
@@ -37059,10 +37069,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -37134,7 +37144,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37153,7 +37163,7 @@
         <v>80</v>
       </c>
       <c r="AI290" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ290" t="s" s="2">
         <v>102</v>
@@ -37176,13 +37186,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37207,7 +37217,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37245,7 +37255,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37272,7 +37282,7 @@
         <v>80</v>
       </c>
       <c r="AI291" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ291" t="s" s="2">
         <v>102</v>
@@ -37295,13 +37305,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37326,7 +37336,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37364,7 +37374,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37391,7 +37401,7 @@
         <v>80</v>
       </c>
       <c r="AI292" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ292" t="s" s="2">
         <v>102</v>
@@ -37414,10 +37424,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37510,7 +37520,7 @@
         <v>90</v>
       </c>
       <c r="AI293" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ293" t="s" s="2">
         <v>102</v>
@@ -37533,10 +37543,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -37562,14 +37572,14 @@
         <v>253</v>
       </c>
       <c r="L294" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="M294" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="N294" s="2"/>
       <c r="O294" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P294" t="s" s="2">
         <v>78</v>
@@ -37618,7 +37628,7 @@
         <v>78</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>79</v>
@@ -37639,10 +37649,10 @@
         <v>78</v>
       </c>
       <c r="AM294" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AN294" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="AO294" t="s" s="2">
         <v>78</v>
@@ -37650,10 +37660,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37765,10 +37775,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37859,7 +37869,7 @@
         <v>80</v>
       </c>
       <c r="AI296" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="AJ296" t="s" s="2">
         <v>119</v>
@@ -37871,7 +37881,7 @@
         <v>78</v>
       </c>
       <c r="AM296" t="s" s="2">
-        <v>108</v>
+        <v>199</v>
       </c>
       <c r="AN296" t="s" s="2">
         <v>78</v>
@@ -37882,10 +37892,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37911,7 +37921,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37982,7 +37992,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -37999,10 +38009,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38028,7 +38038,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38101,7 +38111,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38118,10 +38128,10 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C299" s="2"/>
       <c r="D299" t="s" s="2">
@@ -38147,10 +38157,10 @@
         <v>476</v>
       </c>
       <c r="L299" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="M299" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="N299" s="2"/>
       <c r="O299" s="2"/>
@@ -38201,7 +38211,7 @@
         <v>78</v>
       </c>
       <c r="AF299" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="AG299" t="s" s="2">
         <v>79</v>
@@ -38222,7 +38232,7 @@
         <v>78</v>
       </c>
       <c r="AM299" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AN299" t="s" s="2">
         <v>78</v>
@@ -38233,10 +38243,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38259,19 +38269,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38300,7 +38310,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38318,7 +38328,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38336,10 +38346,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="978">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -686,7 +686,7 @@
     <t>InscriptionOrdre : Eléments permettant de retrouver les informations d'inscription à un ordre par rapport à la profession de la personne physique sur une période et un département donné.</t>
   </si>
   <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true".</t>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la première inscription si "isFirst = true". Ces données sont uniquement accessibles en accès restreint.</t>
   </si>
   <si>
     <t>Practitioner.extension:as-ext-registration.id</t>
@@ -2965,19 +2965,22 @@
     <t>Practitioner.qualification:savoirFaire.code</t>
   </si>
   <si>
+    <t>SavoirFaire.typeSavoirFaire</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
+  </si>
+  <si>
     <t>typeSavoirFaire</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:savoirFaire.code.coding:typeSavoirFaire</t>
   </si>
   <si>
     <t>Le type de savoir-faire (qualifications/autres attributions).
@@ -3014,7 +3017,7 @@
     <t>Starting time with inclusive boundary</t>
   </si>
   <si>
-    <t>dateReconnaissance</t>
+    <t>SavoirFaire.dateReconnaissance</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.period.end</t>
@@ -3023,7 +3026,7 @@
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>dateAbandon</t>
+    <t>SavoirFaire.dateAbandon</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.issuer</t>
@@ -37192,7 +37195,7 @@
         <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37217,7 +37220,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37255,7 +37258,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37305,7 +37308,7 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>891</v>
@@ -37336,7 +37339,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37374,7 +37377,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37424,7 +37427,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>898</v>
@@ -37543,7 +37546,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>829</v>
@@ -37660,7 +37663,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>902</v>
@@ -37775,7 +37778,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>904</v>
@@ -37892,7 +37895,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>906</v>
@@ -37921,7 +37924,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37992,7 +37995,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38009,7 +38012,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>909</v>
@@ -38038,7 +38041,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38111,7 +38114,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38128,7 +38131,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>835</v>
@@ -38243,10 +38246,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38269,19 +38272,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38310,7 +38313,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38328,7 +38331,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38346,10 +38349,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="980">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2794,106 +2794,110 @@
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
+  </si>
+  <si>
+    <t>degreeType</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.coding:degree</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.start</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.start</t>
+  </si>
+  <si>
+    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
+cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.period.end</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.period.end</t>
+  </si>
+  <si>
+    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:degree.issuer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:system}
 </t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degreeType</t>
-  </si>
-  <si>
-    <t>degreeType</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J81-TypeDiplome-RASS/FHIR/JDV-J81-TypeDiplome-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.coding:degree</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Période durant laquelle le niveau de formation est actif.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.start</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.start</t>
-  </si>
-  <si>
-    <t>dateDebut : Date d’obtention du diplôme (dateDiplome)
-cette date est renseignée par l’ordre à la clôture de l’exercice professionnel.</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.period.end</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.period.end</t>
-  </si>
-  <si>
-    <t>dateFin : Date à laquelle le niveau de formation n’est plus actif (non visible hormis dans les données historisées).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:degree.issuer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
-</t>
-  </si>
-  <si>
-    <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro</t>
-  </si>
-  <si>
-    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:exercicePro.code.coding</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
@@ -35043,7 +35047,7 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>892</v>
+        <v>925</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
@@ -35085,13 +35089,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35116,7 +35120,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35154,7 +35158,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35204,7 +35208,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>891</v>
@@ -35235,7 +35239,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35323,7 +35327,7 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B275" t="s" s="2">
         <v>898</v>
@@ -35442,7 +35446,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>829</v>
@@ -35559,7 +35563,7 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B277" t="s" s="2">
         <v>902</v>
@@ -35674,7 +35678,7 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B278" t="s" s="2">
         <v>904</v>
@@ -35791,7 +35795,7 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B279" t="s" s="2">
         <v>906</v>
@@ -35820,7 +35824,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35908,7 +35912,7 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B280" t="s" s="2">
         <v>909</v>
@@ -35937,7 +35941,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36027,7 +36031,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>835</v>
@@ -36142,13 +36146,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>804</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36173,7 +36177,7 @@
         <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>807</v>
@@ -36259,7 +36263,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>812</v>
@@ -36374,7 +36378,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>813</v>
@@ -36491,7 +36495,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>814</v>
@@ -36610,7 +36614,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>819</v>
@@ -36727,7 +36731,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>824</v>
@@ -36823,7 +36827,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
@@ -36840,7 +36844,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>887</v>
@@ -36955,7 +36959,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>889</v>
@@ -37072,7 +37076,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>891</v>
@@ -37147,7 +37151,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>892</v>
+        <v>925</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37189,13 +37193,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37220,7 +37224,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37258,7 +37262,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37308,13 +37312,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37339,7 +37343,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37377,7 +37381,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37427,7 +37431,7 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B293" t="s" s="2">
         <v>898</v>
@@ -37546,7 +37550,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>829</v>
@@ -37663,7 +37667,7 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B295" t="s" s="2">
         <v>902</v>
@@ -37778,7 +37782,7 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B296" t="s" s="2">
         <v>904</v>
@@ -37895,7 +37899,7 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B297" t="s" s="2">
         <v>906</v>
@@ -37924,7 +37928,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37995,7 +37999,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38012,7 +38016,7 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B298" t="s" s="2">
         <v>909</v>
@@ -38041,7 +38045,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38114,7 +38118,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38131,7 +38135,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>835</v>
@@ -38246,10 +38250,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38272,19 +38276,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L300" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="M300" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="N300" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="O300" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38313,7 +38317,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38331,7 +38335,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38349,10 +38353,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AM300" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11058" uniqueCount="979">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2538,7 +2538,7 @@
     <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:code}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -2792,10 +2792,6 @@
   </si>
   <si>
     <t>Practitioner.qualification.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
   </si>
   <si>
     <t>Practitioner.qualification:degree.code.coding:degreeType</t>
@@ -32943,7 +32939,7 @@
         <v>78</v>
       </c>
       <c r="AB254" t="s" s="2">
-        <v>892</v>
+        <v>808</v>
       </c>
       <c r="AC254" s="2"/>
       <c r="AD254" t="s" s="2">
@@ -32985,13 +32981,13 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B255" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>78</v>
@@ -33054,7 +33050,7 @@
       </c>
       <c r="Y255" s="2"/>
       <c r="Z255" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AA255" t="s" s="2">
         <v>78</v>
@@ -33104,7 +33100,7 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B256" t="s" s="2">
         <v>891</v>
@@ -33223,10 +33219,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="B257" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="B257" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -33342,7 +33338,7 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B258" t="s" s="2">
         <v>829</v>
@@ -33371,7 +33367,7 @@
         <v>253</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="M258" t="s" s="2">
         <v>831</v>
@@ -33459,10 +33455,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="B259" t="s" s="2">
         <v>901</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>902</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -33574,10 +33570,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="B260" t="s" s="2">
         <v>903</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>904</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -33691,10 +33687,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="B261" t="s" s="2">
         <v>905</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>906</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -33720,7 +33716,7 @@
         <v>260</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="M261" t="s" s="2">
         <v>262</v>
@@ -33808,10 +33804,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B262" t="s" s="2">
         <v>908</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>909</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -33837,7 +33833,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="s" s="2">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="M262" t="s" s="2">
         <v>271</v>
@@ -33927,7 +33923,7 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>835</v>
@@ -33953,10 +33949,10 @@
         <v>78</v>
       </c>
       <c r="K263" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="L263" t="s" s="2">
         <v>912</v>
-      </c>
-      <c r="L263" t="s" s="2">
-        <v>913</v>
       </c>
       <c r="M263" t="s" s="2">
         <v>837</v>
@@ -34042,13 +34038,13 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>804</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D264" t="s" s="2">
         <v>78</v>
@@ -34073,7 +34069,7 @@
         <v>805</v>
       </c>
       <c r="L264" t="s" s="2">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="M264" t="s" s="2">
         <v>807</v>
@@ -34159,7 +34155,7 @@
     </row>
     <row r="265" hidden="true">
       <c r="A265" t="s" s="2">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B265" t="s" s="2">
         <v>812</v>
@@ -34274,7 +34270,7 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B266" t="s" s="2">
         <v>813</v>
@@ -34391,7 +34387,7 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B267" t="s" s="2">
         <v>814</v>
@@ -34510,7 +34506,7 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B268" t="s" s="2">
         <v>819</v>
@@ -34627,7 +34623,7 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B269" t="s" s="2">
         <v>824</v>
@@ -34740,7 +34736,7 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B270" t="s" s="2">
         <v>887</v>
@@ -34855,7 +34851,7 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B271" t="s" s="2">
         <v>889</v>
@@ -34972,7 +34968,7 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B272" t="s" s="2">
         <v>891</v>
@@ -35047,7 +35043,7 @@
         <v>78</v>
       </c>
       <c r="AB272" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AC272" s="2"/>
       <c r="AD272" t="s" s="2">
@@ -35089,13 +35085,13 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B273" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D273" t="s" s="2">
         <v>78</v>
@@ -35120,7 +35116,7 @@
         <v>154</v>
       </c>
       <c r="L273" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="M273" t="s" s="2">
         <v>395</v>
@@ -35158,7 +35154,7 @@
       </c>
       <c r="Y273" s="2"/>
       <c r="Z273" t="s" s="2">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="AA273" t="s" s="2">
         <v>78</v>
@@ -35208,7 +35204,7 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B274" t="s" s="2">
         <v>891</v>
@@ -35239,7 +35235,7 @@
         <v>154</v>
       </c>
       <c r="L274" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M274" t="s" s="2">
         <v>395</v>
@@ -35327,10 +35323,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -35446,7 +35442,7 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B276" t="s" s="2">
         <v>829</v>
@@ -35563,10 +35559,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -35678,10 +35674,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -35795,10 +35791,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -35824,7 +35820,7 @@
         <v>260</v>
       </c>
       <c r="L279" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="M279" t="s" s="2">
         <v>262</v>
@@ -35912,10 +35908,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -35941,7 +35937,7 @@
         <v>260</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="M280" t="s" s="2">
         <v>271</v>
@@ -36031,7 +36027,7 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B281" t="s" s="2">
         <v>835</v>
@@ -36146,13 +36142,13 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B282" t="s" s="2">
         <v>804</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D282" t="s" s="2">
         <v>78</v>
@@ -36177,7 +36173,7 @@
         <v>805</v>
       </c>
       <c r="L282" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="M282" t="s" s="2">
         <v>807</v>
@@ -36263,7 +36259,7 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B283" t="s" s="2">
         <v>812</v>
@@ -36378,7 +36374,7 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B284" t="s" s="2">
         <v>813</v>
@@ -36495,7 +36491,7 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B285" t="s" s="2">
         <v>814</v>
@@ -36614,7 +36610,7 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B286" t="s" s="2">
         <v>819</v>
@@ -36731,7 +36727,7 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B287" t="s" s="2">
         <v>824</v>
@@ -36827,7 +36823,7 @@
         <v>102</v>
       </c>
       <c r="AK287" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AL287" t="s" s="2">
         <v>78</v>
@@ -36844,7 +36840,7 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B288" t="s" s="2">
         <v>887</v>
@@ -36959,7 +36955,7 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B289" t="s" s="2">
         <v>889</v>
@@ -37076,7 +37072,7 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B290" t="s" s="2">
         <v>891</v>
@@ -37151,7 +37147,7 @@
         <v>78</v>
       </c>
       <c r="AB290" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="AC290" s="2"/>
       <c r="AD290" t="s" s="2">
@@ -37193,13 +37189,13 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B291" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D291" t="s" s="2">
         <v>78</v>
@@ -37224,7 +37220,7 @@
         <v>154</v>
       </c>
       <c r="L291" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M291" t="s" s="2">
         <v>395</v>
@@ -37262,7 +37258,7 @@
       </c>
       <c r="Y291" s="2"/>
       <c r="Z291" t="s" s="2">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="AA291" t="s" s="2">
         <v>78</v>
@@ -37312,13 +37308,13 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B292" t="s" s="2">
         <v>891</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D292" t="s" s="2">
         <v>78</v>
@@ -37343,7 +37339,7 @@
         <v>154</v>
       </c>
       <c r="L292" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="M292" t="s" s="2">
         <v>395</v>
@@ -37381,7 +37377,7 @@
       </c>
       <c r="Y292" s="2"/>
       <c r="Z292" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AA292" t="s" s="2">
         <v>78</v>
@@ -37431,10 +37427,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -37550,7 +37546,7 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B294" t="s" s="2">
         <v>829</v>
@@ -37667,10 +37663,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -37782,10 +37778,10 @@
     </row>
     <row r="296" hidden="true">
       <c r="A296" t="s" s="2">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C296" s="2"/>
       <c r="D296" t="s" s="2">
@@ -37899,10 +37895,10 @@
     </row>
     <row r="297" hidden="true">
       <c r="A297" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C297" s="2"/>
       <c r="D297" t="s" s="2">
@@ -37928,7 +37924,7 @@
         <v>260</v>
       </c>
       <c r="L297" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M297" t="s" s="2">
         <v>262</v>
@@ -37999,7 +37995,7 @@
         <v>102</v>
       </c>
       <c r="AK297" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="AL297" t="s" s="2">
         <v>266</v>
@@ -38016,10 +38012,10 @@
     </row>
     <row r="298" hidden="true">
       <c r="A298" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C298" s="2"/>
       <c r="D298" t="s" s="2">
@@ -38045,7 +38041,7 @@
         <v>260</v>
       </c>
       <c r="L298" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="M298" t="s" s="2">
         <v>271</v>
@@ -38118,7 +38114,7 @@
         <v>102</v>
       </c>
       <c r="AK298" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="AL298" t="s" s="2">
         <v>275</v>
@@ -38135,7 +38131,7 @@
     </row>
     <row r="299" hidden="true">
       <c r="A299" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B299" t="s" s="2">
         <v>835</v>
@@ -38250,10 +38246,10 @@
     </row>
     <row r="300" hidden="true">
       <c r="A300" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="C300" s="2"/>
       <c r="D300" t="s" s="2">
@@ -38276,19 +38272,19 @@
         <v>78</v>
       </c>
       <c r="K300" t="s" s="2">
+        <v>971</v>
+      </c>
+      <c r="L300" t="s" s="2">
         <v>972</v>
       </c>
-      <c r="L300" t="s" s="2">
+      <c r="M300" t="s" s="2">
         <v>973</v>
       </c>
-      <c r="M300" t="s" s="2">
+      <c r="N300" t="s" s="2">
         <v>974</v>
       </c>
-      <c r="N300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>975</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>976</v>
       </c>
       <c r="P300" t="s" s="2">
         <v>78</v>
@@ -38317,7 +38313,7 @@
       </c>
       <c r="Y300" s="2"/>
       <c r="Z300" t="s" s="2">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AA300" t="s" s="2">
         <v>78</v>
@@ -38335,7 +38331,7 @@
         <v>78</v>
       </c>
       <c r="AF300" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AG300" t="s" s="2">
         <v>79</v>
@@ -38353,10 +38349,10 @@
         <v>78</v>
       </c>
       <c r="AL300" t="s" s="2">
+        <v>977</v>
+      </c>
+      <c r="AM300" t="s" s="2">
         <v>978</v>
-      </c>
-      <c r="AM300" t="s" s="2">
-        <v>979</v>
       </c>
       <c r="AN300" t="s" s="2">
         <v>78</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2947,7 +2947,7 @@
     <t>savoirFaire</t>
   </si>
   <si>
-    <t>savoirFAire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
+    <t>savoirFaire : Prérogatives d'exercice d'un professionnel reconnues par une autorité d'enregistrement sur une période donnée de son exercice professionnel, par exemple les spécialités ordinales, etc.</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire.id</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
